--- a/codespace/DetroitRiverCase/results/ch4_fw2_c3_bray_curtis_dissimilarity_matrix.xlsx
+++ b/codespace/DetroitRiverCase/results/ch4_fw2_c3_bray_curtis_dissimilarity_matrix.xlsx
@@ -908,10 +908,10 @@
         <v>0.7587482546674152</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.4747616286361441</v>
+        <v>0.1933646334509404</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.8126796867817176</v>
+        <v>0.8427691473977741</v>
       </c>
     </row>
     <row r="3">
@@ -1092,10 +1092,10 @@
         <v>0.7299234111165853</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.8484615956827495</v>
+        <v>0.9005725177270476</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.7304940764575725</v>
+        <v>0.6673655506178979</v>
       </c>
     </row>
     <row r="4">
@@ -1276,10 +1276,10 @@
         <v>0.8206540739659267</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.492346239490361</v>
+        <v>0.1115743390543482</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.8130364895903736</v>
+        <v>0.830548166942606</v>
       </c>
     </row>
     <row r="5">
@@ -1460,10 +1460,10 @@
         <v>0.6741749607124149</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.8691728248713645</v>
+        <v>0.9072137443511757</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.7442530384538599</v>
+        <v>0.6580514659065023</v>
       </c>
     </row>
     <row r="6">
@@ -1644,10 +1644,10 @@
         <v>0.8378840807015042</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.5222099404967646</v>
+        <v>0.1208448600543346</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.8707494513592965</v>
+        <v>0.857937767436884</v>
       </c>
     </row>
     <row r="7">
@@ -1828,10 +1828,10 @@
         <v>0.7246127366609295</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.4478787237631496</v>
+        <v>0.0931459139441403</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.8103373668943927</v>
+        <v>0.7801693819761908</v>
       </c>
     </row>
     <row r="8">
@@ -2012,10 +2012,10 @@
         <v>0.6500785751702463</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.4478787237631497</v>
+        <v>0.1890920847226265</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.6850075463545015</v>
+        <v>0.7056352204855076</v>
       </c>
     </row>
     <row r="9">
@@ -2196,10 +2196,10 @@
         <v>0.8535033990711448</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.5234745195941429</v>
+        <v>0.4280322515975129</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.8074037074952339</v>
+        <v>0.8238645136601493</v>
       </c>
     </row>
     <row r="10">
@@ -2380,10 +2380,10 @@
         <v>0.6710413080895009</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.4175347132839385</v>
+        <v>0.1892678313469154</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.648474875975985</v>
+        <v>0.7040655587508206</v>
       </c>
     </row>
     <row r="11">
@@ -2564,10 +2564,10 @@
         <v>0.8086463501063076</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.5082416560477866</v>
+        <v>0.1195421757259775</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.8530412511029879</v>
+        <v>0.8703845237320795</v>
       </c>
     </row>
     <row r="12">
@@ -2748,10 +2748,10 @@
         <v>0.7369477911646588</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.5773128881190848</v>
+        <v>0.1337013323799899</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.7387139547429982</v>
+        <v>0.7691723191961836</v>
       </c>
     </row>
     <row r="13">
@@ -2932,10 +2932,10 @@
         <v>0.8054314747913367</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.5089491518413619</v>
+        <v>0.106339861502168</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.8532828403083246</v>
+        <v>0.8697929310804416</v>
       </c>
     </row>
     <row r="14">
@@ -3116,10 +3116,10 @@
         <v>0.7408044877924396</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.5055542961142814</v>
+        <v>0.1731866104944237</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.8522251846809086</v>
+        <v>0.8673467203624435</v>
       </c>
     </row>
     <row r="15">
@@ -3300,10 +3300,10 @@
         <v>0.4519110926464479</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.8243496480135647</v>
+        <v>0.8780536912275191</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.6858502831606809</v>
+        <v>0.389878774952187</v>
       </c>
     </row>
     <row r="16">
@@ -3484,10 +3484,10 @@
         <v>0.8384843722716953</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.5111418013319223</v>
+        <v>0.5088525563819359</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.8609292756968385</v>
+        <v>0.8795482639637685</v>
       </c>
     </row>
     <row r="17">
@@ -3668,10 +3668,10 @@
         <v>0.7008032128514058</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.4499827305696235</v>
+        <v>0.1507898072899141</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.7022403966787365</v>
+        <v>0.756359858166667</v>
       </c>
     </row>
     <row r="18">
@@ -3852,10 +3852,10 @@
         <v>0.748709122203098</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.8763977121454729</v>
+        <v>0.9131868653068752</v>
       </c>
       <c r="BH18" t="n">
-        <v>0.7449916643998252</v>
+        <v>0.7223340931245606</v>
       </c>
     </row>
     <row r="19">
@@ -4036,10 +4036,10 @@
         <v>0.8350426024556024</v>
       </c>
       <c r="BG19" t="n">
-        <v>0.5370095806274249</v>
+        <v>0.3378583198178158</v>
       </c>
       <c r="BH19" t="n">
-        <v>0.8205075966049518</v>
+        <v>0.8494682099188062</v>
       </c>
     </row>
     <row r="20">
@@ -4220,10 +4220,10 @@
         <v>0.8511699610176648</v>
       </c>
       <c r="BG20" t="n">
-        <v>0.533772429557698</v>
+        <v>0.381916910312207</v>
       </c>
       <c r="BH20" t="n">
-        <v>0.875563560516455</v>
+        <v>0.8860800428990766</v>
       </c>
     </row>
     <row r="21">
@@ -4404,10 +4404,10 @@
         <v>0.847592975068471</v>
       </c>
       <c r="BG21" t="n">
-        <v>0.5429049365194722</v>
+        <v>0.1052166617308278</v>
       </c>
       <c r="BH21" t="n">
-        <v>0.8878728388487261</v>
+        <v>0.8958527975289022</v>
       </c>
     </row>
     <row r="22">
@@ -4588,10 +4588,10 @@
         <v>0.6174698795180724</v>
       </c>
       <c r="BG22" t="n">
-        <v>0.8637890284293473</v>
+        <v>0.9106863207126304</v>
       </c>
       <c r="BH22" t="n">
-        <v>0.7310301773461618</v>
+        <v>0.5348921181853646</v>
       </c>
     </row>
     <row r="23">
@@ -4772,10 +4772,10 @@
         <v>0.356790799561884</v>
       </c>
       <c r="BG23" t="n">
-        <v>0.5331632535717692</v>
+        <v>0.5042775478857283</v>
       </c>
       <c r="BH23" t="n">
-        <v>0.693098175161063</v>
+        <v>0.3965183874401484</v>
       </c>
     </row>
     <row r="24">
@@ -4956,10 +4956,10 @@
         <v>0.4457831325301205</v>
       </c>
       <c r="BG24" t="n">
-        <v>0.9445875206934873</v>
+        <v>0.9385962742981551</v>
       </c>
       <c r="BH24" t="n">
-        <v>0.7893170821752764</v>
+        <v>0.539893866464034</v>
       </c>
     </row>
     <row r="25">
@@ -5140,10 +5140,10 @@
         <v>0.3493975903614459</v>
       </c>
       <c r="BG25" t="n">
-        <v>0.5773128881190848</v>
+        <v>0.538596274298155</v>
       </c>
       <c r="BH25" t="n">
-        <v>0.7387139547429981</v>
+        <v>0.4757328523268842</v>
       </c>
     </row>
     <row r="26">
@@ -5324,10 +5324,10 @@
         <v>0.3109360518999074</v>
       </c>
       <c r="BG26" t="n">
-        <v>0.5701291074970587</v>
+        <v>0.5878270400385077</v>
       </c>
       <c r="BH26" t="n">
-        <v>0.7245514916769512</v>
+        <v>0.4623810901840365</v>
       </c>
     </row>
     <row r="27">
@@ -5508,10 +5508,10 @@
         <v>0.8674698795180724</v>
       </c>
       <c r="BG27" t="n">
-        <v>0.5714810116176767</v>
+        <v>0.1231841905410649</v>
       </c>
       <c r="BH27" t="n">
-        <v>0.9267274314802814</v>
+        <v>0.9230265248333335</v>
       </c>
     </row>
     <row r="28">
@@ -5692,10 +5692,10 @@
         <v>0.8932152629302854</v>
       </c>
       <c r="BG28" t="n">
-        <v>0.6182933456430605</v>
+        <v>0.184705863180795</v>
       </c>
       <c r="BH28" t="n">
-        <v>0.9336591721069387</v>
+        <v>0.9254397909618103</v>
       </c>
     </row>
     <row r="29">
@@ -5876,10 +5876,10 @@
         <v>0.8931977911646587</v>
       </c>
       <c r="BG29" t="n">
-        <v>0.6182690982946355</v>
+        <v>0.1846883914151682</v>
       </c>
       <c r="BH29" t="n">
-        <v>0.9336327310779388</v>
+        <v>0.9254223191961836</v>
       </c>
     </row>
     <row r="30">
@@ -6060,10 +6060,10 @@
         <v>0.7036144578313253</v>
       </c>
       <c r="BG30" t="n">
-        <v>0.5773128881190847</v>
+        <v>0.138596274298155</v>
       </c>
       <c r="BH30" t="n">
-        <v>0.7387139547429981</v>
+        <v>0.7358389858628502</v>
       </c>
     </row>
     <row r="31">
@@ -6244,10 +6244,10 @@
         <v>0.6076807228915663</v>
       </c>
       <c r="BG31" t="n">
-        <v>0.5019392989490444</v>
+        <v>0.3252381438677404</v>
       </c>
       <c r="BH31" t="n">
-        <v>0.6779767653669954</v>
+        <v>0.6082244367132003</v>
       </c>
     </row>
     <row r="32">
@@ -6428,10 +6428,10 @@
         <v>0.3132530120481928</v>
       </c>
       <c r="BG32" t="n">
-        <v>0.8637890284293473</v>
+        <v>0.9106863207126307</v>
       </c>
       <c r="BH32" t="n">
-        <v>0.7337703753410534</v>
+        <v>0.3485979102862744</v>
       </c>
     </row>
     <row r="33">
@@ -6612,10 +6612,10 @@
         <v>0.7553203468077919</v>
       </c>
       <c r="BG33" t="n">
-        <v>0.444588406864996</v>
+        <v>0.07962419101895465</v>
       </c>
       <c r="BH33" t="n">
-        <v>0.8123573008584999</v>
+        <v>0.7828396089454832</v>
       </c>
     </row>
     <row r="34">
@@ -6796,10 +6796,10 @@
         <v>0.8674698795180723</v>
       </c>
       <c r="BG34" t="n">
-        <v>0.5714810116176767</v>
+        <v>0.1231841905410648</v>
       </c>
       <c r="BH34" t="n">
-        <v>0.9267274314802814</v>
+        <v>0.9230265248333337</v>
       </c>
     </row>
     <row r="35">
@@ -6980,10 +6980,10 @@
         <v>0.691566265060241</v>
       </c>
       <c r="BG35" t="n">
-        <v>0.876397712145473</v>
+        <v>0.9131868653068748</v>
       </c>
       <c r="BH35" t="n">
-        <v>0.7445007749394386</v>
+        <v>0.6651912359817035</v>
       </c>
     </row>
     <row r="36">
@@ -7164,10 +7164,10 @@
         <v>0.8603270223752153</v>
       </c>
       <c r="BG36" t="n">
-        <v>0.5417424008339834</v>
+        <v>0.2760782292597825</v>
       </c>
       <c r="BH36" t="n">
-        <v>0.8942983404155843</v>
+        <v>0.901597953404762</v>
       </c>
     </row>
     <row r="37">
@@ -7348,10 +7348,10 @@
         <v>0.4457831325301205</v>
       </c>
       <c r="BG37" t="n">
-        <v>0.9445875206934873</v>
+        <v>0.9385962742981551</v>
       </c>
       <c r="BH37" t="n">
-        <v>0.7893170821752764</v>
+        <v>0.539893866464034</v>
       </c>
     </row>
     <row r="38">
@@ -7532,10 +7532,10 @@
         <v>0.4457831325301205</v>
       </c>
       <c r="BG38" t="n">
-        <v>0.9445875206934873</v>
+        <v>0.9385962742981551</v>
       </c>
       <c r="BH38" t="n">
-        <v>0.7893170821752764</v>
+        <v>0.539893866464034</v>
       </c>
     </row>
     <row r="39">
@@ -7716,10 +7716,10 @@
         <v>0.4457831325301205</v>
       </c>
       <c r="BG39" t="n">
-        <v>0.9445875206934873</v>
+        <v>0.9385962742981551</v>
       </c>
       <c r="BH39" t="n">
-        <v>0.7893170821752764</v>
+        <v>0.539893866464034</v>
       </c>
     </row>
     <row r="40">
@@ -7900,10 +7900,10 @@
         <v>0.4191940174491067</v>
       </c>
       <c r="BG40" t="n">
-        <v>0.8398614105574103</v>
+        <v>0.8934449414022856</v>
       </c>
       <c r="BH40" t="n">
-        <v>0.7054286946855283</v>
+        <v>0.3294153739127379</v>
       </c>
     </row>
     <row r="41">
@@ -8084,10 +8084,10 @@
         <v>0.7433734939759037</v>
       </c>
       <c r="BG41" t="n">
-        <v>0.8581961146688932</v>
+        <v>0.9047131997569314</v>
       </c>
       <c r="BH41" t="n">
-        <v>0.7907968509581907</v>
+        <v>0.6709166875004015</v>
       </c>
     </row>
     <row r="42">
@@ -8268,10 +8268,10 @@
         <v>0.8430796356156333</v>
       </c>
       <c r="BG42" t="n">
-        <v>0.5419479152604247</v>
+        <v>0.1084885239956008</v>
       </c>
       <c r="BH42" t="n">
-        <v>0.8970505621407878</v>
+        <v>0.8986362809308946</v>
       </c>
     </row>
     <row r="43">
@@ -8452,10 +8452,10 @@
         <v>0.7620803804150348</v>
       </c>
       <c r="BG43" t="n">
-        <v>0.4938964442550261</v>
+        <v>0.2925728068048299</v>
       </c>
       <c r="BH43" t="n">
-        <v>0.7268243358660217</v>
+        <v>0.6665069278417181</v>
       </c>
     </row>
     <row r="44">
@@ -8636,10 +8636,10 @@
         <v>0.7266082877948001</v>
       </c>
       <c r="BG44" t="n">
-        <v>0.7985141396280689</v>
+        <v>0.8060901755920807</v>
       </c>
       <c r="BH44" t="n">
-        <v>0.5792174490775696</v>
+        <v>0.5520164712254815</v>
       </c>
     </row>
     <row r="45">
@@ -8820,10 +8820,10 @@
         <v>0.7244447402871154</v>
       </c>
       <c r="BG45" t="n">
-        <v>0.6839097406225075</v>
+        <v>0.7792360657455248</v>
       </c>
       <c r="BH45" t="n">
-        <v>0.649064747114988</v>
+        <v>0.585361821681875</v>
       </c>
     </row>
     <row r="46">
@@ -9004,10 +9004,10 @@
         <v>0.8196253404337885</v>
       </c>
       <c r="BG46" t="n">
-        <v>0.5216139045495626</v>
+        <v>0.1180543370567392</v>
       </c>
       <c r="BH46" t="n">
-        <v>0.7679216639413537</v>
+        <v>0.7936727401339296</v>
       </c>
     </row>
     <row r="47">
@@ -9188,10 +9188,10 @@
         <v>0.7969136985317014</v>
       </c>
       <c r="BG47" t="n">
-        <v>0.8159166719638108</v>
+        <v>0.8659395878332171</v>
       </c>
       <c r="BH47" t="n">
-        <v>0.7292030285278347</v>
+        <v>0.686917163401617</v>
       </c>
     </row>
     <row r="48">
@@ -9372,10 +9372,10 @@
         <v>0.8241399964326658</v>
       </c>
       <c r="BG48" t="n">
-        <v>0.6309875267740461</v>
+        <v>0.7355126971790297</v>
       </c>
       <c r="BH48" t="n">
-        <v>0.7344013084922628</v>
+        <v>0.6766259834968884</v>
       </c>
     </row>
     <row r="49">
@@ -9556,10 +9556,10 @@
         <v>0.4075218294200261</v>
       </c>
       <c r="BG49" t="n">
-        <v>0.7942108238782972</v>
+        <v>0.8236478230767402</v>
       </c>
       <c r="BH49" t="n">
-        <v>0.6606267498785225</v>
+        <v>0.3967577599775325</v>
       </c>
     </row>
     <row r="50">
@@ -9740,10 +9740,10 @@
         <v>0.3998093236697137</v>
       </c>
       <c r="BG50" t="n">
-        <v>0.860283485229032</v>
+        <v>0.8783485379829309</v>
       </c>
       <c r="BH50" t="n">
-        <v>0.6096879789957554</v>
+        <v>0.3815363519272131</v>
       </c>
     </row>
     <row r="51">
@@ -9924,10 +9924,10 @@
         <v>0.7318752361361822</v>
       </c>
       <c r="BG51" t="n">
-        <v>0.4483918463807166</v>
+        <v>0.1230700608266778</v>
       </c>
       <c r="BH51" t="n">
-        <v>0.7857736062886433</v>
+        <v>0.8196724112479172</v>
       </c>
     </row>
     <row r="52">
@@ -10108,10 +10108,10 @@
         <v>0.6253646163601775</v>
       </c>
       <c r="BG52" t="n">
-        <v>0.6004544397556913</v>
+        <v>0.671164245596712</v>
       </c>
       <c r="BH52" t="n">
-        <v>0.6076112204582886</v>
+        <v>0.6047830493182924</v>
       </c>
     </row>
     <row r="53">
@@ -10292,10 +10292,10 @@
         <v>0.2619709607661415</v>
       </c>
       <c r="BG53" t="n">
-        <v>0.8103380566088781</v>
+        <v>0.8699830589579843</v>
       </c>
       <c r="BH53" t="n">
-        <v>0.6830301711459451</v>
+        <v>0.3296016532965698</v>
       </c>
     </row>
     <row r="54">
@@ -10476,10 +10476,10 @@
         <v>0.3132530120481926</v>
       </c>
       <c r="BG54" t="n">
-        <v>0.8634679374477265</v>
+        <v>0.9100573530971492</v>
       </c>
       <c r="BH54" t="n">
-        <v>0.7150097441466003</v>
+        <v>0.3362012160713981</v>
       </c>
     </row>
     <row r="55">
@@ -10660,10 +10660,10 @@
         <v>0.602873030583874</v>
       </c>
       <c r="BG55" t="n">
-        <v>0.4530192514490591</v>
+        <v>0.4191008618555165</v>
       </c>
       <c r="BH55" t="n">
-        <v>0.5792943094844507</v>
+        <v>0.6312633609486229</v>
       </c>
     </row>
     <row r="56">
@@ -10844,10 +10844,10 @@
         <v>0.3033520219491828</v>
       </c>
       <c r="BG56" t="n">
-        <v>0.8497273252044361</v>
+        <v>0.9001563629981393</v>
       </c>
       <c r="BH56" t="n">
-        <v>0.7038028984495841</v>
+        <v>0.3517750545828457</v>
       </c>
     </row>
     <row r="57">
@@ -11028,10 +11028,10 @@
         <v>0.2695487833687693</v>
       </c>
       <c r="BG57" t="n">
-        <v>0.6870726305234169</v>
+        <v>0.7596251414686164</v>
       </c>
       <c r="BH57" t="n">
-        <v>0.6729002379638654</v>
+        <v>0.3802894082882314</v>
       </c>
     </row>
     <row r="58">
@@ -11212,10 +11212,10 @@
         <v>0</v>
       </c>
       <c r="BG58" t="n">
-        <v>0.6631563409020635</v>
+        <v>0.7611149320780767</v>
       </c>
       <c r="BH58" t="n">
-        <v>0.6355504862513767</v>
+        <v>0.3036912094948316</v>
       </c>
     </row>
     <row r="59">
@@ -11225,181 +11225,181 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4747616286361441</v>
+        <v>0.1933646334509404</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8484615956827495</v>
+        <v>0.9005725177270476</v>
       </c>
       <c r="D59" t="n">
-        <v>0.492346239490361</v>
+        <v>0.1115743390543482</v>
       </c>
       <c r="E59" t="n">
-        <v>0.8691728248713645</v>
+        <v>0.9072137443511757</v>
       </c>
       <c r="F59" t="n">
-        <v>0.5222099404967646</v>
+        <v>0.1208448600543346</v>
       </c>
       <c r="G59" t="n">
-        <v>0.4478787237631496</v>
+        <v>0.0931459139441403</v>
       </c>
       <c r="H59" t="n">
-        <v>0.4478787237631497</v>
+        <v>0.1890920847226265</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5234745195941429</v>
+        <v>0.4280322515975129</v>
       </c>
       <c r="J59" t="n">
-        <v>0.4175347132839385</v>
+        <v>0.1892678313469154</v>
       </c>
       <c r="K59" t="n">
-        <v>0.5082416560477866</v>
+        <v>0.1195421757259775</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5773128881190848</v>
+        <v>0.1337013323799899</v>
       </c>
       <c r="M59" t="n">
-        <v>0.5089491518413619</v>
+        <v>0.106339861502168</v>
       </c>
       <c r="N59" t="n">
-        <v>0.5055542961142814</v>
+        <v>0.1731866104944237</v>
       </c>
       <c r="O59" t="n">
-        <v>0.8243496480135647</v>
+        <v>0.8780536912275191</v>
       </c>
       <c r="P59" t="n">
-        <v>0.5111418013319223</v>
+        <v>0.5088525563819359</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.4499827305696235</v>
+        <v>0.1507898072899141</v>
       </c>
       <c r="R59" t="n">
-        <v>0.8763977121454729</v>
+        <v>0.9131868653068752</v>
       </c>
       <c r="S59" t="n">
-        <v>0.5370095806274249</v>
+        <v>0.3378583198178158</v>
       </c>
       <c r="T59" t="n">
-        <v>0.533772429557698</v>
+        <v>0.381916910312207</v>
       </c>
       <c r="U59" t="n">
-        <v>0.5429049365194722</v>
+        <v>0.1052166617308278</v>
       </c>
       <c r="V59" t="n">
-        <v>0.8637890284293473</v>
+        <v>0.9106863207126304</v>
       </c>
       <c r="W59" t="n">
-        <v>0.5331632535717692</v>
+        <v>0.5042775478857283</v>
       </c>
       <c r="X59" t="n">
-        <v>0.9445875206934873</v>
+        <v>0.9385962742981551</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.5773128881190848</v>
+        <v>0.538596274298155</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.5701291074970587</v>
+        <v>0.5878270400385077</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.5714810116176767</v>
+        <v>0.1231841905410649</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.6182933456430605</v>
+        <v>0.184705863180795</v>
       </c>
       <c r="AC59" t="n">
-        <v>0.6182690982946355</v>
+        <v>0.1846883914151682</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.5773128881190847</v>
+        <v>0.138596274298155</v>
       </c>
       <c r="AE59" t="n">
-        <v>0.5019392989490444</v>
+        <v>0.3252381438677404</v>
       </c>
       <c r="AF59" t="n">
-        <v>0.8637890284293473</v>
+        <v>0.9106863207126307</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.444588406864996</v>
+        <v>0.07962419101895465</v>
       </c>
       <c r="AH59" t="n">
-        <v>0.5714810116176767</v>
+        <v>0.1231841905410648</v>
       </c>
       <c r="AI59" t="n">
-        <v>0.876397712145473</v>
+        <v>0.9131868653068748</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.5417424008339834</v>
+        <v>0.2760782292597825</v>
       </c>
       <c r="AK59" t="n">
-        <v>0.9445875206934873</v>
+        <v>0.9385962742981551</v>
       </c>
       <c r="AL59" t="n">
-        <v>0.9445875206934873</v>
+        <v>0.9385962742981551</v>
       </c>
       <c r="AM59" t="n">
-        <v>0.9445875206934873</v>
+        <v>0.9385962742981551</v>
       </c>
       <c r="AN59" t="n">
-        <v>0.8398614105574103</v>
+        <v>0.8934449414022856</v>
       </c>
       <c r="AO59" t="n">
-        <v>0.8581961146688932</v>
+        <v>0.9047131997569314</v>
       </c>
       <c r="AP59" t="n">
-        <v>0.5419479152604247</v>
+        <v>0.1084885239956008</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.4938964442550261</v>
+        <v>0.2925728068048299</v>
       </c>
       <c r="AR59" t="n">
-        <v>0.7985141396280689</v>
+        <v>0.8060901755920807</v>
       </c>
       <c r="AS59" t="n">
-        <v>0.6839097406225075</v>
+        <v>0.7792360657455248</v>
       </c>
       <c r="AT59" t="n">
-        <v>0.5216139045495626</v>
+        <v>0.1180543370567392</v>
       </c>
       <c r="AU59" t="n">
-        <v>0.8159166719638108</v>
+        <v>0.8659395878332171</v>
       </c>
       <c r="AV59" t="n">
-        <v>0.6309875267740461</v>
+        <v>0.7355126971790297</v>
       </c>
       <c r="AW59" t="n">
-        <v>0.7942108238782972</v>
+        <v>0.8236478230767402</v>
       </c>
       <c r="AX59" t="n">
-        <v>0.860283485229032</v>
+        <v>0.8783485379829309</v>
       </c>
       <c r="AY59" t="n">
-        <v>0.4483918463807166</v>
+        <v>0.1230700608266778</v>
       </c>
       <c r="AZ59" t="n">
-        <v>0.6004544397556913</v>
+        <v>0.671164245596712</v>
       </c>
       <c r="BA59" t="n">
-        <v>0.8103380566088781</v>
+        <v>0.8699830589579843</v>
       </c>
       <c r="BB59" t="n">
-        <v>0.8634679374477265</v>
+        <v>0.9100573530971492</v>
       </c>
       <c r="BC59" t="n">
-        <v>0.4530192514490591</v>
+        <v>0.4191008618555165</v>
       </c>
       <c r="BD59" t="n">
-        <v>0.8497273252044361</v>
+        <v>0.9001563629981393</v>
       </c>
       <c r="BE59" t="n">
-        <v>0.6870726305234169</v>
+        <v>0.7596251414686164</v>
       </c>
       <c r="BF59" t="n">
-        <v>0.6631563409020635</v>
+        <v>0.7611149320780767</v>
       </c>
       <c r="BG59" t="n">
         <v>0</v>
       </c>
       <c r="BH59" t="n">
-        <v>0.5956134577570164</v>
+        <v>0.8016487885813016</v>
       </c>
     </row>
     <row r="60">
@@ -11409,178 +11409,178 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8126796867817176</v>
+        <v>0.8427691473977741</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7304940764575725</v>
+        <v>0.6673655506178979</v>
       </c>
       <c r="D60" t="n">
-        <v>0.8130364895903736</v>
+        <v>0.830548166942606</v>
       </c>
       <c r="E60" t="n">
-        <v>0.7442530384538599</v>
+        <v>0.6580514659065023</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8707494513592965</v>
+        <v>0.857937767436884</v>
       </c>
       <c r="G60" t="n">
-        <v>0.8103373668943927</v>
+        <v>0.7801693819761908</v>
       </c>
       <c r="H60" t="n">
-        <v>0.6850075463545015</v>
+        <v>0.7056352204855076</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8074037074952339</v>
+        <v>0.8238645136601493</v>
       </c>
       <c r="J60" t="n">
-        <v>0.648474875975985</v>
+        <v>0.7040655587508206</v>
       </c>
       <c r="K60" t="n">
-        <v>0.8530412511029879</v>
+        <v>0.8703845237320795</v>
       </c>
       <c r="L60" t="n">
-        <v>0.7387139547429982</v>
+        <v>0.7691723191961836</v>
       </c>
       <c r="M60" t="n">
-        <v>0.8532828403083246</v>
+        <v>0.8697929310804416</v>
       </c>
       <c r="N60" t="n">
-        <v>0.8522251846809086</v>
+        <v>0.8673467203624435</v>
       </c>
       <c r="O60" t="n">
-        <v>0.6858502831606809</v>
+        <v>0.389878774952187</v>
       </c>
       <c r="P60" t="n">
-        <v>0.8609292756968385</v>
+        <v>0.8795482639637685</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.7022403966787365</v>
+        <v>0.756359858166667</v>
       </c>
       <c r="R60" t="n">
-        <v>0.7449916643998252</v>
+        <v>0.7223340931245606</v>
       </c>
       <c r="S60" t="n">
-        <v>0.8205075966049518</v>
+        <v>0.8494682099188062</v>
       </c>
       <c r="T60" t="n">
-        <v>0.875563560516455</v>
+        <v>0.8860800428990766</v>
       </c>
       <c r="U60" t="n">
-        <v>0.8878728388487261</v>
+        <v>0.8958527975289022</v>
       </c>
       <c r="V60" t="n">
-        <v>0.7310301773461618</v>
+        <v>0.5348921181853646</v>
       </c>
       <c r="W60" t="n">
-        <v>0.693098175161063</v>
+        <v>0.3965183874401484</v>
       </c>
       <c r="X60" t="n">
-        <v>0.7893170821752764</v>
+        <v>0.539893866464034</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.7387139547429981</v>
+        <v>0.4757328523268842</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.7245514916769512</v>
+        <v>0.4623810901840365</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.9267274314802814</v>
+        <v>0.9230265248333335</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.9336591721069387</v>
+        <v>0.9254397909618103</v>
       </c>
       <c r="AC60" t="n">
-        <v>0.9336327310779388</v>
+        <v>0.9254223191961836</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.7387139547429981</v>
+        <v>0.7358389858628502</v>
       </c>
       <c r="AE60" t="n">
-        <v>0.6779767653669954</v>
+        <v>0.6082244367132003</v>
       </c>
       <c r="AF60" t="n">
-        <v>0.7337703753410534</v>
+        <v>0.3485979102862744</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.8123573008584999</v>
+        <v>0.7828396089454832</v>
       </c>
       <c r="AH60" t="n">
-        <v>0.9267274314802814</v>
+        <v>0.9230265248333337</v>
       </c>
       <c r="AI60" t="n">
-        <v>0.7445007749394386</v>
+        <v>0.6651912359817035</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.8942983404155843</v>
+        <v>0.901597953404762</v>
       </c>
       <c r="AK60" t="n">
-        <v>0.7893170821752764</v>
+        <v>0.539893866464034</v>
       </c>
       <c r="AL60" t="n">
-        <v>0.7893170821752764</v>
+        <v>0.539893866464034</v>
       </c>
       <c r="AM60" t="n">
-        <v>0.7893170821752764</v>
+        <v>0.539893866464034</v>
       </c>
       <c r="AN60" t="n">
-        <v>0.7054286946855283</v>
+        <v>0.3294153739127379</v>
       </c>
       <c r="AO60" t="n">
-        <v>0.7907968509581907</v>
+        <v>0.6709166875004015</v>
       </c>
       <c r="AP60" t="n">
-        <v>0.8970505621407878</v>
+        <v>0.8986362809308946</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.7268243358660217</v>
+        <v>0.6665069278417181</v>
       </c>
       <c r="AR60" t="n">
-        <v>0.5792174490775696</v>
+        <v>0.5520164712254815</v>
       </c>
       <c r="AS60" t="n">
-        <v>0.649064747114988</v>
+        <v>0.585361821681875</v>
       </c>
       <c r="AT60" t="n">
-        <v>0.7679216639413537</v>
+        <v>0.7936727401339296</v>
       </c>
       <c r="AU60" t="n">
-        <v>0.7292030285278347</v>
+        <v>0.686917163401617</v>
       </c>
       <c r="AV60" t="n">
-        <v>0.7344013084922628</v>
+        <v>0.6766259834968884</v>
       </c>
       <c r="AW60" t="n">
-        <v>0.6606267498785225</v>
+        <v>0.3967577599775325</v>
       </c>
       <c r="AX60" t="n">
-        <v>0.6096879789957554</v>
+        <v>0.3815363519272131</v>
       </c>
       <c r="AY60" t="n">
-        <v>0.7857736062886433</v>
+        <v>0.8196724112479172</v>
       </c>
       <c r="AZ60" t="n">
-        <v>0.6076112204582886</v>
+        <v>0.6047830493182924</v>
       </c>
       <c r="BA60" t="n">
-        <v>0.6830301711459451</v>
+        <v>0.3296016532965698</v>
       </c>
       <c r="BB60" t="n">
-        <v>0.7150097441466003</v>
+        <v>0.3362012160713981</v>
       </c>
       <c r="BC60" t="n">
-        <v>0.5792943094844507</v>
+        <v>0.6312633609486229</v>
       </c>
       <c r="BD60" t="n">
-        <v>0.7038028984495841</v>
+        <v>0.3517750545828457</v>
       </c>
       <c r="BE60" t="n">
-        <v>0.6729002379638654</v>
+        <v>0.3802894082882314</v>
       </c>
       <c r="BF60" t="n">
-        <v>0.6355504862513767</v>
+        <v>0.3036912094948316</v>
       </c>
       <c r="BG60" t="n">
-        <v>0.5956134577570164</v>
+        <v>0.8016487885813016</v>
       </c>
       <c r="BH60" t="n">
         <v>0</v>
